--- a/data/trans_orig/ED_ADU-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ED_ADU-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media del adulto entrevistado</t>
+          <t>Edad media del adulto entrevistado (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,58; 43,7</t>
+          <t>39,56; 43,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,47; 45,55</t>
+          <t>41,59; 45,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,7; 45,62</t>
+          <t>41,78; 45,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,31; 49,32</t>
+          <t>43,53; 49,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,32; 45,8</t>
+          <t>41,39; 45,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,28; 47,45</t>
+          <t>43,23; 47,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,88; 48,33</t>
+          <t>43,84; 48,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,1; 52,32</t>
+          <t>48,36; 52,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41,14; 44,07</t>
+          <t>41,05; 44,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,03; 46,05</t>
+          <t>42,91; 45,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,33; 46,38</t>
+          <t>43,46; 46,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,52; 50,16</t>
+          <t>46,35; 50,1</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,03; 45,13</t>
+          <t>42,08; 45,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,11; 46,43</t>
+          <t>43,2; 46,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,47; 47,53</t>
+          <t>44,42; 47,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,48; 48,06</t>
+          <t>43,35; 47,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,63; 47,05</t>
+          <t>43,9; 47,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,72; 48,76</t>
+          <t>45,57; 48,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,51; 50,02</t>
+          <t>46,7; 50,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,63; 52,82</t>
+          <t>49,66; 52,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,36; 45,71</t>
+          <t>43,45; 45,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,82; 47,2</t>
+          <t>44,93; 47,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,09; 48,4</t>
+          <t>46,03; 48,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,08; 49,98</t>
+          <t>47,07; 49,91</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,72; 45,52</t>
+          <t>41,58; 45,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,98; 47,15</t>
+          <t>43,11; 47,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,54; 49,28</t>
+          <t>45,7; 49,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,36; 51,65</t>
+          <t>47,26; 51,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,91; 49,94</t>
+          <t>46,14; 50,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,79; 49,91</t>
+          <t>45,83; 50,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,24; 51,35</t>
+          <t>47,1; 51,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,34; 52,25</t>
+          <t>48,25; 52,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,44; 47,41</t>
+          <t>44,33; 47,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,93; 47,89</t>
+          <t>45,13; 48,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,98; 49,86</t>
+          <t>46,91; 49,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,37; 51,51</t>
+          <t>48,46; 51,44</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,76; 44,37</t>
+          <t>40,74; 44,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,47; 47,39</t>
+          <t>43,64; 47,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,37; 48,15</t>
+          <t>44,07; 47,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,79; 53,48</t>
+          <t>47,42; 53,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,28; 47,25</t>
+          <t>43,75; 47,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,55; 49,37</t>
+          <t>45,46; 49,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,27; 51,52</t>
+          <t>47,29; 51,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,92; 51,63</t>
+          <t>42,7; 51,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,69; 45,4</t>
+          <t>42,71; 45,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,1; 47,79</t>
+          <t>45,18; 47,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,37; 49,29</t>
+          <t>46,32; 49,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,41; 51,6</t>
+          <t>44,81; 51,51</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,58; 45,36</t>
+          <t>40,58; 45,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,99; 47,02</t>
+          <t>41,87; 47,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,08; 49,41</t>
+          <t>45,04; 49,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,6; 51,28</t>
+          <t>46,64; 51,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,72; 47,56</t>
+          <t>42,09; 47,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,46; 49,45</t>
+          <t>44,48; 49,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,29; 53,27</t>
+          <t>48,28; 53,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,81; 53,26</t>
+          <t>46,79; 53,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,05; 45,67</t>
+          <t>41,95; 45,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,72; 47,3</t>
+          <t>44,07; 47,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,34; 50,7</t>
+          <t>47,24; 50,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,52; 51,74</t>
+          <t>47,55; 52,03</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,79; 46,23</t>
+          <t>41,93; 46,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,22; 47,66</t>
+          <t>43,01; 47,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,84; 49,26</t>
+          <t>44,93; 49,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47,15; 51,51</t>
+          <t>47,03; 51,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,78; 49,64</t>
+          <t>44,82; 49,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,52; 50,98</t>
+          <t>46,43; 51,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,7; 51,4</t>
+          <t>46,35; 51,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,45; 51,67</t>
+          <t>47,53; 51,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,09; 47,14</t>
+          <t>44,1; 47,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45,44; 48,88</t>
+          <t>45,41; 48,79</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46,33; 49,7</t>
+          <t>46,43; 49,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47,85; 50,9</t>
+          <t>47,86; 50,88</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,7; 45,85</t>
+          <t>42,79; 45,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,52; 46,36</t>
+          <t>43,37; 46,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,1; 47,06</t>
+          <t>44,12; 46,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,84; 50,7</t>
+          <t>46,88; 50,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,63; 47,43</t>
+          <t>44,54; 47,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,45; 48,36</t>
+          <t>45,7; 48,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,02; 48,92</t>
+          <t>45,91; 48,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48,77; 59,86</t>
+          <t>48,58; 60,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,15; 46,27</t>
+          <t>44,11; 46,12</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,06; 47,02</t>
+          <t>45,0; 47,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45,49; 47,6</t>
+          <t>45,49; 47,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,56; 57,48</t>
+          <t>48,51; 57,0</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,34; 44,92</t>
+          <t>42,32; 44,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,24; 45,8</t>
+          <t>43,19; 45,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,77; 47,25</t>
+          <t>44,81; 47,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47,95; 50,53</t>
+          <t>47,83; 50,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,4; 46,93</t>
+          <t>44,32; 47,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,27; 47,86</t>
+          <t>45,17; 47,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,72; 49,47</t>
+          <t>46,82; 49,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,64; 52,16</t>
+          <t>49,6; 52,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43,67; 45,59</t>
+          <t>43,72; 45,61</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44,65; 46,56</t>
+          <t>44,71; 46,55</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,12; 47,96</t>
+          <t>46,08; 47,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,07; 50,84</t>
+          <t>49,03; 50,78</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42,78; 44,02</t>
+          <t>42,79; 44,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44,12; 45,39</t>
+          <t>44,16; 45,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45,43; 46,6</t>
+          <t>45,43; 46,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47,74; 49,38</t>
+          <t>47,7; 49,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,13; 46,39</t>
+          <t>45,11; 46,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,41; 47,64</t>
+          <t>46,43; 47,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,57; 48,89</t>
+          <t>47,66; 48,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49,73; 53,93</t>
+          <t>49,79; 53,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44,15; 45,09</t>
+          <t>44,17; 45,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45,5; 46,38</t>
+          <t>45,48; 46,36</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46,71; 47,6</t>
+          <t>46,73; 47,57</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49,09; 51,75</t>
+          <t>49,09; 51,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_ADU-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ED_ADU-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46,67</t>
+          <t>47,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>50,35</t>
+          <t>49,39</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,44</t>
+          <t>48,67</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,56; 43,75</t>
+          <t>39,76; 43,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,59; 45,66</t>
+          <t>41,39; 45,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,78; 45,72</t>
+          <t>41,62; 45,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,53; 49,41</t>
+          <t>45,49; 50,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,39; 45,99</t>
+          <t>41,31; 46,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,23; 47,5</t>
+          <t>43,12; 47,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,84; 48,24</t>
+          <t>43,64; 48,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,36; 52,33</t>
+          <t>47,45; 51,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41,05; 44,11</t>
+          <t>41,0; 44,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,91; 45,98</t>
+          <t>42,88; 45,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,46; 46,29</t>
+          <t>43,43; 46,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,35; 50,1</t>
+          <t>47,25; 50,14</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45,83</t>
+          <t>46,81</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,36</t>
+          <t>51,15</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,59</t>
+          <t>49,01</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,08; 45,19</t>
+          <t>42,03; 45,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,2; 46,57</t>
+          <t>43,34; 46,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,42; 47,63</t>
+          <t>44,35; 47,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,35; 47,98</t>
+          <t>44,78; 49,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,9; 47,09</t>
+          <t>43,84; 47,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,57; 48,82</t>
+          <t>45,75; 48,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,7; 50,13</t>
+          <t>46,57; 49,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,66; 52,89</t>
+          <t>49,38; 52,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,45; 45,68</t>
+          <t>43,48; 45,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,93; 47,34</t>
+          <t>44,84; 47,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,03; 48,31</t>
+          <t>46,1; 48,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,07; 49,91</t>
+          <t>47,71; 50,33</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49,5</t>
+          <t>49,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,37</t>
+          <t>50,14</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,96</t>
+          <t>49,77</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,58; 45,58</t>
+          <t>41,31; 45,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,11; 47,34</t>
+          <t>43,11; 47,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,7; 49,39</t>
+          <t>45,52; 49,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,26; 51,57</t>
+          <t>47,27; 51,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,14; 50,09</t>
+          <t>46,03; 50,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,83; 50,09</t>
+          <t>45,47; 49,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,1; 51,19</t>
+          <t>47,03; 51,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,25; 52,31</t>
+          <t>48,34; 52,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,33; 47,26</t>
+          <t>44,35; 47,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,13; 48,06</t>
+          <t>45,04; 47,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,91; 49,87</t>
+          <t>46,91; 49,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,46; 51,44</t>
+          <t>48,34; 51,17</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50,65</t>
+          <t>49,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,46</t>
+          <t>50,51</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,33</t>
+          <t>50,22</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,74; 44,18</t>
+          <t>40,87; 44,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,64; 47,47</t>
+          <t>43,59; 47,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,07; 47,9</t>
+          <t>44,39; 48,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,42; 53,31</t>
+          <t>46,94; 52,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,75; 47,42</t>
+          <t>43,7; 47,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,46; 49,36</t>
+          <t>45,39; 49,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,29; 51,55</t>
+          <t>47,36; 51,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,7; 51,6</t>
+          <t>48,42; 52,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,71; 45,39</t>
+          <t>42,73; 45,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,18; 47,79</t>
+          <t>45,09; 47,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,32; 49,28</t>
+          <t>46,37; 49,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,81; 51,51</t>
+          <t>48,39; 51,67</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49,15</t>
+          <t>48,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50,7</t>
+          <t>51,84</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50,06</t>
+          <t>50,15</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,58; 45,35</t>
+          <t>40,8; 45,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,87; 47,13</t>
+          <t>42,02; 46,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,04; 49,56</t>
+          <t>45,08; 49,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,64; 51,5</t>
+          <t>45,85; 50,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,09; 47,44</t>
+          <t>41,91; 47,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,48; 49,69</t>
+          <t>44,43; 49,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,28; 53,4</t>
+          <t>48,2; 53,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,79; 53,48</t>
+          <t>49,64; 53,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41,95; 45,48</t>
+          <t>42,02; 45,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,07; 47,9</t>
+          <t>43,82; 47,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,24; 50,69</t>
+          <t>47,17; 50,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,55; 52,03</t>
+          <t>48,58; 51,71</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49,16</t>
+          <t>49,31</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49,64</t>
+          <t>49,76</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,4</t>
+          <t>49,53</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,93; 46,24</t>
+          <t>41,85; 46,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,01; 47,81</t>
+          <t>43,54; 48,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,93; 49,46</t>
+          <t>45,1; 49,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47,03; 51,37</t>
+          <t>47,2; 51,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,82; 49,53</t>
+          <t>44,97; 49,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,43; 51,06</t>
+          <t>46,49; 51,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,35; 51,29</t>
+          <t>46,54; 51,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,53; 51,68</t>
+          <t>47,48; 51,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,1; 47,24</t>
+          <t>44,03; 47,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45,41; 48,79</t>
+          <t>45,36; 48,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46,43; 49,87</t>
+          <t>46,51; 49,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47,86; 50,88</t>
+          <t>48,04; 51,07</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48,87</t>
+          <t>49,15</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>53,45</t>
+          <t>49,41</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,51</t>
+          <t>49,29</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,79; 45,76</t>
+          <t>42,74; 45,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,37; 46,39</t>
+          <t>43,47; 46,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,12; 46,92</t>
+          <t>44,12; 46,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,88; 50,62</t>
+          <t>47,31; 50,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,54; 47,39</t>
+          <t>44,62; 47,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,7; 48,39</t>
+          <t>45,57; 48,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,91; 48,78</t>
+          <t>45,81; 48,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48,58; 60,27</t>
+          <t>47,95; 50,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,11; 46,12</t>
+          <t>44,12; 46,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,0; 47,07</t>
+          <t>44,99; 47,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45,49; 47,54</t>
+          <t>45,54; 47,52</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,51; 57,0</t>
+          <t>48,1; 50,38</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49,33</t>
+          <t>48,11</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50,88</t>
+          <t>50,37</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50,0</t>
+          <t>49,26</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,32; 44,93</t>
+          <t>42,38; 44,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,19; 45,75</t>
+          <t>43,19; 45,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,81; 47,29</t>
+          <t>44,79; 47,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47,83; 50,51</t>
+          <t>46,65; 49,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,32; 47,05</t>
+          <t>44,35; 46,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,17; 47,8</t>
+          <t>45,14; 47,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,82; 49,39</t>
+          <t>46,76; 49,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,6; 52,2</t>
+          <t>49,08; 51,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43,72; 45,61</t>
+          <t>43,78; 45,55</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44,71; 46,55</t>
+          <t>44,6; 46,33</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,08; 47,98</t>
+          <t>46,09; 48,01</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,03; 50,78</t>
+          <t>48,31; 50,2</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48,59</t>
+          <t>48,51</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>51,04</t>
+          <t>50,24</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,86</t>
+          <t>49,4</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42,79; 44,04</t>
+          <t>42,8; 44,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44,16; 45,35</t>
+          <t>44,1; 45,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45,43; 46,58</t>
+          <t>45,4; 46,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47,7; 49,36</t>
+          <t>47,8; 49,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,11; 46,39</t>
+          <t>45,18; 46,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,43; 47,66</t>
+          <t>46,43; 47,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,66; 48,92</t>
+          <t>47,6; 48,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49,79; 53,85</t>
+          <t>49,65; 50,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44,17; 45,06</t>
+          <t>44,13; 45,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45,48; 46,36</t>
+          <t>45,56; 46,41</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46,73; 47,57</t>
+          <t>46,76; 47,64</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49,09; 51,61</t>
+          <t>48,96; 49,88</t>
         </is>
       </c>
     </row>
